--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1612,6 +1612,330 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121719451</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97074</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fyrsjötorp 700m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>582432</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6559041</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121719460</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97071</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fyrsjötorp 700m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>582432</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6559041</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121719493</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97069</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fyrsjötorp 700m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582488</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6559024</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687768</v>
+        <v>121687746</v>
       </c>
       <c r="B2" t="n">
-        <v>105218</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R2" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -900,17 +900,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687746</v>
+        <v>121687740</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>94778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R4" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687758</v>
+        <v>121687768</v>
       </c>
       <c r="B5" t="n">
-        <v>97073</v>
+        <v>105218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687752</v>
+        <v>121687738</v>
       </c>
       <c r="B6" t="n">
-        <v>97070</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,31 +1151,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582390</v>
+        <v>582485</v>
       </c>
       <c r="R6" t="n">
-        <v>6558991</v>
+        <v>6559004</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1218,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,17 +1251,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687738</v>
+        <v>121687758</v>
       </c>
       <c r="B7" t="n">
-        <v>92039</v>
+        <v>97073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1270,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582485</v>
+        <v>582390</v>
       </c>
       <c r="R7" t="n">
-        <v>6559004</v>
+        <v>6558991</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1491,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687743</v>
+        <v>121687752</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>97070</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719451</v>
+        <v>121719460</v>
       </c>
       <c r="B11" t="n">
-        <v>97074</v>
+        <v>97071</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224358</v>
+        <v>224364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719460</v>
+        <v>121719451</v>
       </c>
       <c r="B12" t="n">
-        <v>97071</v>
+        <v>97074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224364</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687746</v>
+        <v>121687740</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>94778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R2" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687749</v>
+        <v>121687746</v>
       </c>
       <c r="B3" t="n">
-        <v>97070</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687740</v>
+        <v>121687738</v>
       </c>
       <c r="B4" t="n">
-        <v>94778</v>
+        <v>92039</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,31 +919,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582390</v>
+        <v>582485</v>
       </c>
       <c r="R4" t="n">
-        <v>6558991</v>
+        <v>6559004</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1139,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687738</v>
+        <v>121687755</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>97073</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,48 +1154,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R6" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687755</v>
+        <v>121687752</v>
       </c>
       <c r="B8" t="n">
-        <v>97073</v>
+        <v>97070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,16 +1398,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1407,32 +1415,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R8" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687752</v>
+        <v>121687749</v>
       </c>
       <c r="B9" t="n">
         <v>97070</v>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R9" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719460</v>
+        <v>121719451</v>
       </c>
       <c r="B11" t="n">
-        <v>97071</v>
+        <v>97074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224364</v>
+        <v>224358</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719451</v>
+        <v>121719460</v>
       </c>
       <c r="B12" t="n">
-        <v>97074</v>
+        <v>97071</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224358</v>
+        <v>224364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687738</v>
+        <v>121687758</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
+        <v>97073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582485</v>
+        <v>582390</v>
       </c>
       <c r="R4" t="n">
-        <v>6559004</v>
+        <v>6558991</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687768</v>
+        <v>121687752</v>
       </c>
       <c r="B5" t="n">
-        <v>105218</v>
+        <v>97070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1142,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687755</v>
+        <v>121687738</v>
       </c>
       <c r="B6" t="n">
-        <v>97073</v>
+        <v>92039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,53 +1151,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R6" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687758</v>
+        <v>121687755</v>
       </c>
       <c r="B7" t="n">
         <v>97073</v>
@@ -1299,24 +1291,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R7" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687752</v>
+        <v>121687768</v>
       </c>
       <c r="B8" t="n">
-        <v>97070</v>
+        <v>105218</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719493</v>
+        <v>121719451</v>
       </c>
       <c r="B10" t="n">
-        <v>97069</v>
+        <v>97074</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>224358</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R10" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719451</v>
+        <v>121719493</v>
       </c>
       <c r="B11" t="n">
-        <v>97074</v>
+        <v>97069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R11" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687740</v>
+        <v>121687768</v>
       </c>
       <c r="B2" t="n">
-        <v>94778</v>
+        <v>105218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687746</v>
+        <v>121687752</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>97070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R3" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687758</v>
+        <v>121687746</v>
       </c>
       <c r="B4" t="n">
-        <v>97073</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R4" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687752</v>
+        <v>121687738</v>
       </c>
       <c r="B5" t="n">
-        <v>97070</v>
+        <v>92039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582390</v>
+        <v>582485</v>
       </c>
       <c r="R5" t="n">
-        <v>6558991</v>
+        <v>6559004</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1102,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687738</v>
+        <v>121687740</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>94778</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1154,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582485</v>
+        <v>582390</v>
       </c>
       <c r="R6" t="n">
-        <v>6559004</v>
+        <v>6558991</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687768</v>
+        <v>121687749</v>
       </c>
       <c r="B8" t="n">
-        <v>105218</v>
+        <v>97070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R8" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687749</v>
+        <v>121687758</v>
       </c>
       <c r="B9" t="n">
-        <v>97070</v>
+        <v>97073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R9" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719451</v>
+        <v>121719493</v>
       </c>
       <c r="B10" t="n">
-        <v>97074</v>
+        <v>97069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R10" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719493</v>
+        <v>121719460</v>
       </c>
       <c r="B11" t="n">
-        <v>97069</v>
+        <v>97071</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224363</v>
+        <v>224364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R11" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719460</v>
+        <v>121719451</v>
       </c>
       <c r="B12" t="n">
-        <v>97071</v>
+        <v>97074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224364</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -784,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687752</v>
+        <v>121687755</v>
       </c>
       <c r="B3" t="n">
-        <v>97070</v>
+        <v>97073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -824,24 +824,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R3" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,17 +908,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687746</v>
+        <v>121687752</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>97070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R4" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,17 +1024,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687738</v>
+        <v>121687758</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
+        <v>97073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582485</v>
+        <v>582390</v>
       </c>
       <c r="R5" t="n">
-        <v>6559004</v>
+        <v>6558991</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,17 +1140,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687740</v>
+        <v>121687749</v>
       </c>
       <c r="B6" t="n">
-        <v>94778</v>
+        <v>97070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R6" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,17 +1256,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687755</v>
+        <v>121687746</v>
       </c>
       <c r="B7" t="n">
-        <v>97073</v>
+        <v>97067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,16 +1279,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,22 +1296,14 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1345,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,17 +1372,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687749</v>
+        <v>121687738</v>
       </c>
       <c r="B8" t="n">
-        <v>97070</v>
+        <v>92039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,31 +1391,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R8" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687758</v>
+        <v>121687740</v>
       </c>
       <c r="B9" t="n">
-        <v>97073</v>
+        <v>94778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719493</v>
+        <v>121719460</v>
       </c>
       <c r="B10" t="n">
-        <v>97069</v>
+        <v>97071</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>224364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R10" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719460</v>
+        <v>121719451</v>
       </c>
       <c r="B11" t="n">
-        <v>97071</v>
+        <v>97074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224364</v>
+        <v>224358</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719451</v>
+        <v>121719493</v>
       </c>
       <c r="B12" t="n">
-        <v>97074</v>
+        <v>97069</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R12" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687768</v>
+        <v>121687743</v>
       </c>
       <c r="B2" t="n">
-        <v>105218</v>
+        <v>94778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -908,17 +908,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687752</v>
+        <v>121687758</v>
       </c>
       <c r="B4" t="n">
-        <v>97070</v>
+        <v>97073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687758</v>
+        <v>121687749</v>
       </c>
       <c r="B5" t="n">
-        <v>97073</v>
+        <v>97070</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R5" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,14 +1140,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687749</v>
+        <v>121687752</v>
       </c>
       <c r="B6" t="n">
         <v>97070</v>
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R6" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687746</v>
+        <v>121687768</v>
       </c>
       <c r="B7" t="n">
-        <v>97067</v>
+        <v>105218</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R7" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,17 +1372,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687738</v>
+        <v>121687746</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1391,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R8" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,17 +1488,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687740</v>
+        <v>121687738</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>92039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,31 +1507,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582390</v>
+        <v>582485</v>
       </c>
       <c r="R9" t="n">
-        <v>6558991</v>
+        <v>6559004</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719460</v>
+        <v>121719493</v>
       </c>
       <c r="B10" t="n">
-        <v>97071</v>
+        <v>97069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224364</v>
+        <v>224363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R10" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719493</v>
+        <v>121719460</v>
       </c>
       <c r="B12" t="n">
-        <v>97069</v>
+        <v>97071</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>224364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R12" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -1379,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687746</v>
+        <v>121687738</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>92039</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,31 +1391,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R8" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687738</v>
+        <v>121687746</v>
       </c>
       <c r="B9" t="n">
-        <v>92039</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,34 +1510,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R9" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687743</v>
+        <v>121687755</v>
       </c>
       <c r="B2" t="n">
-        <v>94778</v>
+        <v>97091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R2" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,17 +792,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687755</v>
+        <v>121687740</v>
       </c>
       <c r="B3" t="n">
-        <v>97073</v>
+        <v>94796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,49 +815,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R3" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,17 +908,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687758</v>
+        <v>121687752</v>
       </c>
       <c r="B4" t="n">
-        <v>97073</v>
+        <v>97088</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687749</v>
+        <v>121687738</v>
       </c>
       <c r="B5" t="n">
-        <v>97070</v>
+        <v>92053</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,31 +1043,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R5" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,17 +1143,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687752</v>
+        <v>121687768</v>
       </c>
       <c r="B6" t="n">
-        <v>97070</v>
+        <v>105236</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1166,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1256,17 +1259,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687768</v>
+        <v>121687758</v>
       </c>
       <c r="B7" t="n">
-        <v>105218</v>
+        <v>97091</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,21 +1282,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1342,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,17 +1375,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687738</v>
+        <v>121687749</v>
       </c>
       <c r="B8" t="n">
-        <v>92039</v>
+        <v>97088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1394,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R8" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1501,7 +1501,7 @@
         <v>121687746</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,17 +1607,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719493</v>
+        <v>121719460</v>
       </c>
       <c r="B10" t="n">
-        <v>97069</v>
+        <v>97089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>224364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R10" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719451</v>
+        <v>121719493</v>
       </c>
       <c r="B11" t="n">
-        <v>97074</v>
+        <v>97087</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R11" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719460</v>
+        <v>121719451</v>
       </c>
       <c r="B12" t="n">
-        <v>97071</v>
+        <v>97092</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224364</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687755</v>
+        <v>121687740</v>
       </c>
       <c r="B2" t="n">
-        <v>97091</v>
+        <v>94798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R2" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687740</v>
+        <v>121687746</v>
       </c>
       <c r="B3" t="n">
-        <v>94796</v>
+        <v>97087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R3" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,17 +900,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687752</v>
+        <v>121687738</v>
       </c>
       <c r="B4" t="n">
-        <v>97088</v>
+        <v>92055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,31 +919,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582390</v>
+        <v>582485</v>
       </c>
       <c r="R4" t="n">
-        <v>6558991</v>
+        <v>6559004</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,17 +1019,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687738</v>
+        <v>121687749</v>
       </c>
       <c r="B5" t="n">
-        <v>92053</v>
+        <v>97090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,34 +1038,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R5" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,17 +1135,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687768</v>
+        <v>121687752</v>
       </c>
       <c r="B6" t="n">
-        <v>105236</v>
+        <v>97090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1259,17 +1251,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687758</v>
+        <v>121687755</v>
       </c>
       <c r="B7" t="n">
-        <v>97091</v>
+        <v>97093</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,24 +1291,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R7" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687749</v>
+        <v>121687768</v>
       </c>
       <c r="B8" t="n">
-        <v>97088</v>
+        <v>105238</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R8" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687746</v>
+        <v>121687758</v>
       </c>
       <c r="B9" t="n">
-        <v>97085</v>
+        <v>97093</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R9" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
         <v>121719460</v>
       </c>
       <c r="B10" t="n">
-        <v>97089</v>
+        <v>97091</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719493</v>
+        <v>121719451</v>
       </c>
       <c r="B11" t="n">
-        <v>97087</v>
+        <v>97094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224363</v>
+        <v>224358</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R11" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719451</v>
+        <v>121719493</v>
       </c>
       <c r="B12" t="n">
-        <v>97092</v>
+        <v>97089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224358</v>
+        <v>224363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R12" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687740</v>
+        <v>121687768</v>
       </c>
       <c r="B2" t="n">
-        <v>94798</v>
+        <v>105245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687746</v>
+        <v>121687758</v>
       </c>
       <c r="B3" t="n">
-        <v>97087</v>
+        <v>97100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R3" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687738</v>
+        <v>121687746</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>97094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +919,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R4" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687749</v>
+        <v>121687738</v>
       </c>
       <c r="B5" t="n">
-        <v>97090</v>
+        <v>92056</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,31 +1035,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R5" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687752</v>
+        <v>121687749</v>
       </c>
       <c r="B6" t="n">
-        <v>97090</v>
+        <v>97097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R6" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687755</v>
+        <v>121687743</v>
       </c>
       <c r="B7" t="n">
-        <v>97093</v>
+        <v>94805</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,49 +1274,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R7" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121687768</v>
+        <v>121687755</v>
       </c>
       <c r="B8" t="n">
-        <v>105238</v>
+        <v>97100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,41 +1390,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R8" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687758</v>
+        <v>121687752</v>
       </c>
       <c r="B9" t="n">
-        <v>97093</v>
+        <v>97097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,7 +1617,7 @@
         <v>121719460</v>
       </c>
       <c r="B10" t="n">
-        <v>97091</v>
+        <v>97098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>121719451</v>
       </c>
       <c r="B11" t="n">
-        <v>97094</v>
+        <v>97101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>121719493</v>
       </c>
       <c r="B12" t="n">
-        <v>97089</v>
+        <v>97096</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687768</v>
+        <v>121687758</v>
       </c>
       <c r="B2" t="n">
-        <v>105245</v>
+        <v>97100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687758</v>
+        <v>121687768</v>
       </c>
       <c r="B3" t="n">
-        <v>97100</v>
+        <v>105245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687738</v>
+        <v>121687749</v>
       </c>
       <c r="B5" t="n">
-        <v>92056</v>
+        <v>97097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,34 +1035,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582485</v>
+        <v>582391</v>
       </c>
       <c r="R5" t="n">
-        <v>6559004</v>
+        <v>6558966</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121687749</v>
+        <v>121687738</v>
       </c>
       <c r="B6" t="n">
-        <v>97097</v>
+        <v>92056</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,31 +1151,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582391</v>
+        <v>582485</v>
       </c>
       <c r="R6" t="n">
-        <v>6558966</v>
+        <v>6559004</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 53285-2024 artfynd.xlsx
+++ b/artfynd/A 53285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121687758</v>
+        <v>121687749</v>
       </c>
       <c r="B2" t="n">
-        <v>97100</v>
+        <v>97106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R2" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121687768</v>
+        <v>121687743</v>
       </c>
       <c r="B3" t="n">
-        <v>105245</v>
+        <v>94814</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121687746</v>
+        <v>121687768</v>
       </c>
       <c r="B4" t="n">
-        <v>97094</v>
+        <v>105254</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R4" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121687749</v>
+        <v>121687752</v>
       </c>
       <c r="B5" t="n">
-        <v>97097</v>
+        <v>97106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582391</v>
+        <v>582390</v>
       </c>
       <c r="R5" t="n">
-        <v>6558966</v>
+        <v>6558991</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1142,7 @@
         <v>121687738</v>
       </c>
       <c r="B6" t="n">
-        <v>92056</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121687743</v>
+        <v>121687758</v>
       </c>
       <c r="B7" t="n">
-        <v>94805</v>
+        <v>97109</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
         <v>121687755</v>
       </c>
       <c r="B8" t="n">
-        <v>97100</v>
+        <v>97109</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121687752</v>
+        <v>121687746</v>
       </c>
       <c r="B9" t="n">
-        <v>97097</v>
+        <v>97103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582390</v>
+        <v>582391</v>
       </c>
       <c r="R9" t="n">
-        <v>6558991</v>
+        <v>6558966</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121719460</v>
+        <v>121719493</v>
       </c>
       <c r="B10" t="n">
-        <v>97098</v>
+        <v>97105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224364</v>
+        <v>224363</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582432</v>
+        <v>582488</v>
       </c>
       <c r="R10" t="n">
-        <v>6559041</v>
+        <v>6559024</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121719451</v>
+        <v>121719460</v>
       </c>
       <c r="B11" t="n">
-        <v>97101</v>
+        <v>97107</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224358</v>
+        <v>224364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
+          <t>Lycopodium clavatum subsp. clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121719493</v>
+        <v>121719451</v>
       </c>
       <c r="B12" t="n">
-        <v>97096</v>
+        <v>97110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224363</v>
+        <v>224358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Lycopodium complanatum subsp. complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582488</v>
+        <v>582432</v>
       </c>
       <c r="R12" t="n">
-        <v>6559024</v>
+        <v>6559041</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
